--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122748147</v>
+        <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>91460</v>
+        <v>92913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>937</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storflobodarna V, Ög</t>
+          <t>Bogestad, Bogestad, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566417</v>
+        <v>566413</v>
       </c>
       <c r="R3" t="n">
-        <v>6515477</v>
+        <v>6515479</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,72 +871,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122748147</t>
+          <t>https://artportalen.se/Sighting/136895595</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131493353</v>
+        <v>122748147</v>
       </c>
       <c r="B4" t="n">
-        <v>92571</v>
+        <v>91460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1965</v>
+        <v>937</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Citronporing</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antrodiella citrinella</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Ryvarden</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bogestad, Ög</t>
+          <t>Storflobodarna V, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566514</v>
+        <v>566417</v>
       </c>
       <c r="R4" t="n">
-        <v>6515489</v>
+        <v>6515477</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,88 +967,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131493353</t>
+          <t>https://artportalen.se/Sighting/122748147</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92746900</v>
+        <v>131493353</v>
       </c>
       <c r="B5" t="n">
-        <v>104628</v>
+        <v>92571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>1965</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Citronporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Antrodiella citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>Niemelä &amp; Ryvarden</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bogestad SV 385 m, Ög</t>
+          <t>Bogestad, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566260</v>
+        <v>566514</v>
       </c>
       <c r="R5" t="n">
-        <v>6515488</v>
+        <v>6515489</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-04-24</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,29 +1080,148 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Förefaller vara en 40-årig "granåker"</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan-Erik Axelsson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131493353</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>92746900</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bogestad SV 385 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566260</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6515488</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Förefaller vara en 40-årig "granåker"</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan-Erik Axelsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92746900</t>
         </is>
@@ -1131,6 +1233,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92913</v>
+        <v>92915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18491-2023 artfynd.xlsx
+++ b/artfynd/A 18491-2023 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136895595</v>
       </c>
       <c r="B3" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
